--- a/nr-update-reference-range/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/nr-update-reference-range/ig/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T08:20:47+00:00</t>
+    <t>2026-03-19T08:22:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
